--- a/Versão5/ABNT/Ontologia_15965_0M.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_0M.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D58099-B203-454B-A74A-5CD42749389B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -3468,14 +3468,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F29EE3D7-EE2C-4826-A6E3-4917652068E2}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="65.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>274</v>
       </c>
@@ -3486,7 +3486,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>291</v>
       </c>
@@ -3497,7 +3497,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
         <v>292</v>
       </c>
@@ -3508,7 +3508,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>275</v>
       </c>
@@ -3519,7 +3519,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>276</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>277</v>
       </c>
@@ -3543,7 +3543,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>278</v>
       </c>
@@ -3554,7 +3554,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="46" t="s">
         <v>279</v>
       </c>
@@ -3565,7 +3565,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>293</v>
       </c>
@@ -3576,7 +3576,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>295</v>
       </c>
@@ -3587,7 +3587,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>297</v>
       </c>
@@ -3598,7 +3598,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>280</v>
       </c>
@@ -3609,7 +3609,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>298</v>
       </c>
@@ -3620,7 +3620,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>299</v>
       </c>
@@ -3631,7 +3631,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>300</v>
       </c>
@@ -3642,7 +3642,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>301</v>
       </c>
@@ -3653,7 +3653,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
         <v>284</v>
       </c>
@@ -3664,19 +3664,19 @@
         <v>688</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
         <v>302</v>
       </c>
       <c r="B18" s="14">
         <f ca="1">NOW()</f>
-        <v>46148.628486458336</v>
+        <v>46157.684502199074</v>
       </c>
       <c r="C18" s="49" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>698</v>
       </c>
@@ -3687,7 +3687,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="46" t="s">
         <v>692</v>
       </c>
@@ -3699,7 +3699,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="46" t="s">
         <v>699</v>
       </c>
@@ -3711,7 +3711,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
         <v>290</v>
       </c>
@@ -3722,7 +3722,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
         <v>303</v>
       </c>
@@ -3733,7 +3733,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
         <v>308</v>
       </c>
@@ -3744,7 +3744,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
         <v>309</v>
       </c>
@@ -3755,7 +3755,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="46" t="s">
         <v>684</v>
       </c>
@@ -3775,34 +3775,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90560E5E-B24A-4842-BB96-871B06FB9DEB}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA19"/>
-  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.6640625" style="34" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.69921875" style="34" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7" style="34" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.83203125" style="34" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.33203125" style="34" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" style="34" customWidth="1"/>
+    <col min="4" max="4" width="7.796875" style="34" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.296875" style="34" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.69921875" style="34" customWidth="1"/>
     <col min="7" max="11" width="8.5" style="34" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="60.1640625" customWidth="1"/>
-    <col min="17" max="17" width="55.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="60.19921875" customWidth="1"/>
+    <col min="17" max="17" width="55.19921875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="5" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.296875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.69921875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.19921875" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="3.83203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="79.33203125" style="45" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="3.796875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="79.296875" style="45" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>621</v>
       </c>
@@ -3885,7 +3885,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="51">
         <v>2</v>
       </c>
@@ -3976,7 +3976,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="51">
         <v>3</v>
       </c>
@@ -4067,7 +4067,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="51">
         <v>4</v>
       </c>
@@ -4158,7 +4158,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="51">
         <v>5</v>
       </c>
@@ -4249,7 +4249,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="51">
         <v>6</v>
       </c>
@@ -4340,7 +4340,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="51">
         <v>7</v>
       </c>
@@ -4431,7 +4431,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="51">
         <v>8</v>
       </c>
@@ -4522,7 +4522,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="51">
         <v>9</v>
       </c>
@@ -4613,7 +4613,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="51">
         <v>10</v>
       </c>
@@ -4704,7 +4704,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="51">
         <v>11</v>
       </c>
@@ -4795,7 +4795,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="51">
         <v>12</v>
       </c>
@@ -4886,7 +4886,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="51">
         <v>13</v>
       </c>
@@ -4977,7 +4977,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="51">
         <v>14</v>
       </c>
@@ -5068,7 +5068,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="51">
         <v>15</v>
       </c>
@@ -5159,7 +5159,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="51">
         <v>16</v>
       </c>
@@ -5250,7 +5250,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="51">
         <v>17</v>
       </c>
@@ -5341,7 +5341,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="51">
         <v>18</v>
       </c>
@@ -5432,7 +5432,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="51">
         <v>19</v>
       </c>
@@ -5548,13 +5548,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D0A35A2-CC4F-42BF-87DA-AD07A1ABC76B}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.5" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="5.5" defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="21" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
         <v>622</v>
       </c>
@@ -5619,7 +5619,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="25">
         <v>2</v>
       </c>
@@ -5702,13 +5702,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04D71245-A72D-43F9-AF51-CBBC9C7FE697}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="3" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="2.69921875" customWidth="1"/>
+    <col min="2" max="3" width="12.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="28">
         <v>1</v>
       </c>
@@ -5719,7 +5719,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="19">
         <v>2</v>
       </c>
@@ -5744,37 +5744,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79BA5E7-BFBD-4AC9-B36C-B9776AA17B75}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:Y299"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.19921875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.796875" style="1" customWidth="1"/>
     <col min="5" max="5" width="7.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="5" style="39" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" style="39" customWidth="1"/>
+    <col min="7" max="7" width="8.69921875" style="39" customWidth="1"/>
     <col min="8" max="8" width="5" style="39" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.83203125" style="39" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.796875" style="39" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5" style="39" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.1640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.19921875" style="39" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5.5" style="39" customWidth="1"/>
-    <col min="13" max="13" width="26.1640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26.19921875" style="39" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="7" style="39" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="32.5" style="39" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.1640625" style="39" customWidth="1"/>
+    <col min="16" max="16" width="9.19921875" style="39" customWidth="1"/>
     <col min="17" max="17" width="10.5" style="39" customWidth="1"/>
     <col min="18" max="18" width="9" style="39" customWidth="1"/>
     <col min="19" max="19" width="25.5" style="39" customWidth="1"/>
-    <col min="20" max="20" width="6.6640625" style="39" customWidth="1"/>
-    <col min="21" max="21" width="8.83203125" style="39" customWidth="1"/>
-    <col min="22" max="22" width="7.6640625" style="39" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="25.83203125" style="39" customWidth="1"/>
+    <col min="20" max="20" width="6.69921875" style="39" customWidth="1"/>
+    <col min="21" max="21" width="8.796875" style="39" customWidth="1"/>
+    <col min="22" max="22" width="7.69921875" style="39" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="25.796875" style="39" customWidth="1"/>
     <col min="24" max="24" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.69921875" style="1" bestFit="1" customWidth="1"/>
     <col min="26" max="16384" width="11.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" ht="20.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>304</v>
       </c>
@@ -5851,7 +5851,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>2</v>
       </c>
@@ -5928,7 +5928,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -6005,7 +6005,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>4</v>
       </c>
@@ -6082,7 +6082,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>5</v>
       </c>
@@ -6159,7 +6159,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>6</v>
       </c>
@@ -6236,7 +6236,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>7</v>
       </c>
@@ -6313,7 +6313,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>8</v>
       </c>
@@ -6390,7 +6390,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>9</v>
       </c>
@@ -6467,7 +6467,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>10</v>
       </c>
@@ -6544,7 +6544,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>11</v>
       </c>
@@ -6621,7 +6621,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>12</v>
       </c>
@@ -6698,7 +6698,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>13</v>
       </c>
@@ -6775,7 +6775,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>14</v>
       </c>
@@ -6852,7 +6852,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>15</v>
       </c>
@@ -6929,7 +6929,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>16</v>
       </c>
@@ -7006,7 +7006,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>17</v>
       </c>
@@ -7083,7 +7083,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>18</v>
       </c>
@@ -7160,7 +7160,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>19</v>
       </c>
@@ -7237,7 +7237,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>20</v>
       </c>
@@ -7314,7 +7314,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>21</v>
       </c>
@@ -7391,7 +7391,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>22</v>
       </c>
@@ -7468,7 +7468,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>23</v>
       </c>
@@ -7545,7 +7545,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>24</v>
       </c>
@@ -7622,7 +7622,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>25</v>
       </c>
@@ -7699,7 +7699,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>26</v>
       </c>
@@ -7776,7 +7776,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>27</v>
       </c>
@@ -7853,7 +7853,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>28</v>
       </c>
@@ -7930,7 +7930,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>29</v>
       </c>
@@ -8007,7 +8007,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>30</v>
       </c>
@@ -8084,7 +8084,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>31</v>
       </c>
@@ -8161,7 +8161,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>32</v>
       </c>
@@ -8238,7 +8238,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>33</v>
       </c>
@@ -8315,7 +8315,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>34</v>
       </c>
@@ -8392,7 +8392,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>35</v>
       </c>
@@ -8469,7 +8469,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>36</v>
       </c>
@@ -8546,7 +8546,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>37</v>
       </c>
@@ -8623,7 +8623,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>38</v>
       </c>
@@ -8700,7 +8700,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>39</v>
       </c>
@@ -8777,7 +8777,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>40</v>
       </c>
@@ -8854,7 +8854,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>41</v>
       </c>
@@ -8931,7 +8931,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>42</v>
       </c>
@@ -9008,7 +9008,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>43</v>
       </c>
@@ -9085,7 +9085,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>44</v>
       </c>
@@ -9162,7 +9162,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>45</v>
       </c>
@@ -9239,7 +9239,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>46</v>
       </c>
@@ -9316,7 +9316,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>47</v>
       </c>
@@ -9393,7 +9393,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>48</v>
       </c>
@@ -9470,7 +9470,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>49</v>
       </c>
@@ -9547,7 +9547,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>50</v>
       </c>
@@ -9624,7 +9624,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>51</v>
       </c>
@@ -9701,7 +9701,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>52</v>
       </c>
@@ -9778,7 +9778,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>53</v>
       </c>
@@ -9855,7 +9855,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>54</v>
       </c>
@@ -9932,7 +9932,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>55</v>
       </c>
@@ -10009,7 +10009,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>56</v>
       </c>
@@ -10086,7 +10086,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>57</v>
       </c>
@@ -10163,7 +10163,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>58</v>
       </c>
@@ -10240,7 +10240,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>59</v>
       </c>
@@ -10317,7 +10317,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>60</v>
       </c>
@@ -10394,7 +10394,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>61</v>
       </c>
@@ -10471,7 +10471,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>62</v>
       </c>
@@ -10548,7 +10548,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>63</v>
       </c>
@@ -10625,7 +10625,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>64</v>
       </c>
@@ -10702,7 +10702,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>65</v>
       </c>
@@ -10779,7 +10779,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>66</v>
       </c>
@@ -10856,7 +10856,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>67</v>
       </c>
@@ -10933,7 +10933,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>68</v>
       </c>
@@ -11010,7 +11010,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>69</v>
       </c>
@@ -11087,7 +11087,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>70</v>
       </c>
@@ -11164,7 +11164,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>71</v>
       </c>
@@ -11241,7 +11241,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>72</v>
       </c>
@@ -11318,7 +11318,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>73</v>
       </c>
@@ -11395,7 +11395,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>74</v>
       </c>
@@ -11472,7 +11472,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>75</v>
       </c>
@@ -11549,7 +11549,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>76</v>
       </c>
@@ -11626,7 +11626,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>77</v>
       </c>
@@ -11703,7 +11703,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>78</v>
       </c>
@@ -11780,7 +11780,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>79</v>
       </c>
@@ -11857,7 +11857,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>80</v>
       </c>
@@ -11934,7 +11934,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>81</v>
       </c>
@@ -12011,7 +12011,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>82</v>
       </c>
@@ -12088,7 +12088,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>83</v>
       </c>
@@ -12165,7 +12165,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>84</v>
       </c>
@@ -12242,7 +12242,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>85</v>
       </c>
@@ -12319,7 +12319,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>86</v>
       </c>
@@ -12396,7 +12396,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>87</v>
       </c>
@@ -12473,7 +12473,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>88</v>
       </c>
@@ -12550,7 +12550,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>89</v>
       </c>
@@ -12627,7 +12627,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>90</v>
       </c>
@@ -12704,7 +12704,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>91</v>
       </c>
@@ -12781,7 +12781,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>92</v>
       </c>
@@ -12858,7 +12858,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>93</v>
       </c>
@@ -12935,7 +12935,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>94</v>
       </c>
@@ -13012,7 +13012,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>95</v>
       </c>
@@ -13089,7 +13089,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>96</v>
       </c>
@@ -13166,7 +13166,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>97</v>
       </c>
@@ -13243,7 +13243,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>98</v>
       </c>
@@ -13320,7 +13320,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>99</v>
       </c>
@@ -13397,7 +13397,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>100</v>
       </c>
@@ -13474,7 +13474,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>101</v>
       </c>
@@ -13551,7 +13551,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>102</v>
       </c>
@@ -13628,7 +13628,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>103</v>
       </c>
@@ -13705,7 +13705,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>104</v>
       </c>
@@ -13782,7 +13782,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>105</v>
       </c>
@@ -13859,7 +13859,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>106</v>
       </c>
@@ -13936,7 +13936,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>107</v>
       </c>
@@ -14013,7 +14013,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>108</v>
       </c>
@@ -14090,7 +14090,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>109</v>
       </c>
@@ -14167,7 +14167,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>110</v>
       </c>
@@ -14244,7 +14244,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>111</v>
       </c>
@@ -14321,7 +14321,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>112</v>
       </c>
@@ -14398,7 +14398,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>113</v>
       </c>
@@ -14475,7 +14475,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>114</v>
       </c>
@@ -14552,7 +14552,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>115</v>
       </c>
@@ -14629,7 +14629,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>116</v>
       </c>
@@ -14706,7 +14706,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>117</v>
       </c>
@@ -14783,7 +14783,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>118</v>
       </c>
@@ -14860,7 +14860,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>119</v>
       </c>
@@ -14937,7 +14937,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>120</v>
       </c>
@@ -15014,7 +15014,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>121</v>
       </c>
@@ -15091,7 +15091,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>122</v>
       </c>
@@ -15168,7 +15168,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="123" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>123</v>
       </c>
@@ -15245,7 +15245,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>124</v>
       </c>
@@ -15322,7 +15322,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>125</v>
       </c>
@@ -15399,7 +15399,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>126</v>
       </c>
@@ -15476,7 +15476,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>127</v>
       </c>
@@ -15553,7 +15553,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>128</v>
       </c>
@@ -15630,7 +15630,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="129" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>129</v>
       </c>
@@ -15707,7 +15707,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="130" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>130</v>
       </c>
@@ -15784,7 +15784,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="131" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>131</v>
       </c>
@@ -15861,7 +15861,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="132" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>132</v>
       </c>
@@ -15938,7 +15938,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="133" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>133</v>
       </c>
@@ -16015,7 +16015,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="134" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>134</v>
       </c>
@@ -16092,7 +16092,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="135" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>135</v>
       </c>
@@ -16169,7 +16169,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>136</v>
       </c>
@@ -16246,7 +16246,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>137</v>
       </c>
@@ -16323,7 +16323,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>138</v>
       </c>
@@ -16400,7 +16400,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>139</v>
       </c>
@@ -16477,7 +16477,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>140</v>
       </c>
@@ -16554,7 +16554,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>141</v>
       </c>
@@ -16631,7 +16631,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="142" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>142</v>
       </c>
@@ -16708,7 +16708,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="143" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>143</v>
       </c>
@@ -16785,7 +16785,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="144" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>144</v>
       </c>
@@ -16862,7 +16862,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>145</v>
       </c>
@@ -16939,7 +16939,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="146" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>146</v>
       </c>
@@ -17016,7 +17016,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="147" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>147</v>
       </c>
@@ -17093,7 +17093,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="148" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>148</v>
       </c>
@@ -17170,7 +17170,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="149" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>149</v>
       </c>
@@ -17247,7 +17247,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>150</v>
       </c>
@@ -17324,7 +17324,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="151" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>151</v>
       </c>
@@ -17401,7 +17401,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="152" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>152</v>
       </c>
@@ -17478,7 +17478,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="153" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
         <v>153</v>
       </c>
@@ -17555,7 +17555,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>154</v>
       </c>
@@ -17632,7 +17632,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="155" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>155</v>
       </c>
@@ -17709,7 +17709,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="156" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
         <v>156</v>
       </c>
@@ -17786,7 +17786,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="157" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>157</v>
       </c>
@@ -17863,7 +17863,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="158" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>158</v>
       </c>
@@ -17940,7 +17940,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="159" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
         <v>159</v>
       </c>
@@ -18017,7 +18017,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="160" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
         <v>160</v>
       </c>
@@ -18094,7 +18094,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="161" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
         <v>161</v>
       </c>
@@ -18171,7 +18171,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="162" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
         <v>162</v>
       </c>
@@ -18248,7 +18248,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="163" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
         <v>163</v>
       </c>
@@ -18325,7 +18325,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="164" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
         <v>164</v>
       </c>
@@ -18402,7 +18402,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="165" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
         <v>165</v>
       </c>
@@ -18479,7 +18479,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="166" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
         <v>166</v>
       </c>
@@ -18556,7 +18556,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="167" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
         <v>167</v>
       </c>
@@ -18633,7 +18633,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="168" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
         <v>168</v>
       </c>
@@ -18710,7 +18710,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="169" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
         <v>169</v>
       </c>
@@ -18787,7 +18787,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="170" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
         <v>170</v>
       </c>
@@ -18864,7 +18864,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="171" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
         <v>171</v>
       </c>
@@ -18941,7 +18941,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="172" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2">
         <v>172</v>
       </c>
@@ -19018,7 +19018,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="173" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
         <v>173</v>
       </c>
@@ -19095,7 +19095,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="174" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
         <v>174</v>
       </c>
@@ -19172,7 +19172,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="175" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2">
         <v>175</v>
       </c>
@@ -19249,7 +19249,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="176" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
         <v>176</v>
       </c>
@@ -19326,7 +19326,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="177" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
         <v>177</v>
       </c>
@@ -19403,7 +19403,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="178" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
         <v>178</v>
       </c>
@@ -19480,7 +19480,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="179" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2">
         <v>179</v>
       </c>
@@ -19557,7 +19557,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="180" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2">
         <v>180</v>
       </c>
@@ -19634,7 +19634,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="181" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2">
         <v>181</v>
       </c>
@@ -19711,7 +19711,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="182" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
         <v>182</v>
       </c>
@@ -19788,7 +19788,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="183" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
         <v>183</v>
       </c>
@@ -19865,7 +19865,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="184" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2">
         <v>184</v>
       </c>
@@ -19942,7 +19942,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="185" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2">
         <v>185</v>
       </c>
@@ -20019,7 +20019,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="186" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
         <v>186</v>
       </c>
@@ -20096,7 +20096,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="187" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
         <v>187</v>
       </c>
@@ -20173,7 +20173,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="188" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
         <v>188</v>
       </c>
@@ -20250,7 +20250,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="189" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2">
         <v>189</v>
       </c>
@@ -20327,7 +20327,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="190" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2">
         <v>190</v>
       </c>
@@ -20404,7 +20404,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="191" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2">
         <v>191</v>
       </c>
@@ -20481,7 +20481,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="192" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2">
         <v>192</v>
       </c>
@@ -20558,7 +20558,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="193" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
         <v>193</v>
       </c>
@@ -20635,7 +20635,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="194" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
         <v>194</v>
       </c>
@@ -20712,7 +20712,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="195" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2">
         <v>195</v>
       </c>
@@ -20789,7 +20789,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="196" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2">
         <v>196</v>
       </c>
@@ -20866,7 +20866,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="197" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
         <v>197</v>
       </c>
@@ -20943,7 +20943,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="198" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2">
         <v>198</v>
       </c>
@@ -21020,7 +21020,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="199" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2">
         <v>199</v>
       </c>
@@ -21097,7 +21097,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="200" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2">
         <v>200</v>
       </c>
@@ -21174,7 +21174,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="201" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2">
         <v>201</v>
       </c>
@@ -21251,7 +21251,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="202" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2">
         <v>202</v>
       </c>
@@ -21328,7 +21328,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="203" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2">
         <v>203</v>
       </c>
@@ -21405,7 +21405,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="204" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2">
         <v>204</v>
       </c>
@@ -21482,7 +21482,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="205" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2">
         <v>205</v>
       </c>
@@ -21559,7 +21559,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="206" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2">
         <v>206</v>
       </c>
@@ -21636,7 +21636,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="207" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2">
         <v>207</v>
       </c>
@@ -21713,7 +21713,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="208" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
         <v>208</v>
       </c>
@@ -21790,7 +21790,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="209" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2">
         <v>209</v>
       </c>
@@ -21867,7 +21867,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="210" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2">
         <v>210</v>
       </c>
@@ -21944,7 +21944,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="211" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2">
         <v>211</v>
       </c>
@@ -22021,7 +22021,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="212" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
         <v>212</v>
       </c>
@@ -22098,7 +22098,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="213" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2">
         <v>213</v>
       </c>
@@ -22175,7 +22175,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="214" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2">
         <v>214</v>
       </c>
@@ -22252,7 +22252,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="215" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2">
         <v>215</v>
       </c>
@@ -22329,7 +22329,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="216" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2">
         <v>216</v>
       </c>
@@ -22406,7 +22406,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="217" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2">
         <v>217</v>
       </c>
@@ -22483,7 +22483,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="218" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
         <v>218</v>
       </c>
@@ -22560,7 +22560,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="219" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2">
         <v>219</v>
       </c>
@@ -22637,7 +22637,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="220" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2">
         <v>220</v>
       </c>
@@ -22714,7 +22714,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="221" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2">
         <v>221</v>
       </c>
@@ -22791,7 +22791,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="222" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
         <v>222</v>
       </c>
@@ -22868,7 +22868,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="223" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2">
         <v>223</v>
       </c>
@@ -22945,7 +22945,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="224" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2">
         <v>224</v>
       </c>
@@ -23022,7 +23022,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="225" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2">
         <v>225</v>
       </c>
@@ -23099,7 +23099,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="226" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2">
         <v>226</v>
       </c>
@@ -23176,7 +23176,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="227" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2">
         <v>227</v>
       </c>
@@ -23253,7 +23253,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="228" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2">
         <v>228</v>
       </c>
@@ -23330,7 +23330,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="229" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2">
         <v>229</v>
       </c>
@@ -23407,7 +23407,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="230" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2">
         <v>230</v>
       </c>
@@ -23484,7 +23484,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="231" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2">
         <v>231</v>
       </c>
@@ -23561,7 +23561,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="232" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2">
         <v>232</v>
       </c>
@@ -23638,7 +23638,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="233" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2">
         <v>233</v>
       </c>
@@ -23715,7 +23715,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="234" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2">
         <v>234</v>
       </c>
@@ -23792,7 +23792,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="235" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2">
         <v>235</v>
       </c>
@@ -23869,7 +23869,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="236" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2">
         <v>236</v>
       </c>
@@ -23946,7 +23946,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="237" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2">
         <v>237</v>
       </c>
@@ -24023,7 +24023,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="238" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2">
         <v>238</v>
       </c>
@@ -24100,7 +24100,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="239" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2">
         <v>239</v>
       </c>
@@ -24177,7 +24177,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="240" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2">
         <v>240</v>
       </c>
@@ -24254,7 +24254,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="241" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2">
         <v>241</v>
       </c>
@@ -24331,7 +24331,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="242" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2">
         <v>242</v>
       </c>
@@ -24408,7 +24408,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="243" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2">
         <v>243</v>
       </c>
@@ -24485,7 +24485,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="244" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2">
         <v>244</v>
       </c>
@@ -24562,7 +24562,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="245" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2">
         <v>245</v>
       </c>
@@ -24639,7 +24639,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="246" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2">
         <v>246</v>
       </c>
@@ -24716,7 +24716,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="247" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2">
         <v>247</v>
       </c>
@@ -24793,7 +24793,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="248" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2">
         <v>248</v>
       </c>
@@ -24870,7 +24870,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="249" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2">
         <v>249</v>
       </c>
@@ -24947,7 +24947,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="250" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2">
         <v>250</v>
       </c>
@@ -25024,7 +25024,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="251" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2">
         <v>251</v>
       </c>
@@ -25101,7 +25101,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="252" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2">
         <v>252</v>
       </c>
@@ -25178,7 +25178,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="253" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2">
         <v>253</v>
       </c>
@@ -25255,7 +25255,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="254" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2">
         <v>254</v>
       </c>
@@ -25332,7 +25332,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="255" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2">
         <v>255</v>
       </c>
@@ -25409,7 +25409,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="256" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2">
         <v>256</v>
       </c>
@@ -25486,7 +25486,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="257" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2">
         <v>257</v>
       </c>
@@ -25563,7 +25563,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="258" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2">
         <v>258</v>
       </c>
@@ -25640,7 +25640,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="259" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2">
         <v>259</v>
       </c>
@@ -25717,7 +25717,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="260" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2">
         <v>260</v>
       </c>
@@ -25794,7 +25794,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="261" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2">
         <v>261</v>
       </c>
@@ -25871,7 +25871,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="262" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2">
         <v>262</v>
       </c>
@@ -25948,7 +25948,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="263" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2">
         <v>263</v>
       </c>
@@ -26025,7 +26025,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="264" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2">
         <v>264</v>
       </c>
@@ -26102,7 +26102,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="265" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2">
         <v>265</v>
       </c>
@@ -26179,7 +26179,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="266" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2">
         <v>266</v>
       </c>
@@ -26256,7 +26256,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="267" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2">
         <v>267</v>
       </c>
@@ -26333,7 +26333,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="268" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2">
         <v>268</v>
       </c>
@@ -26410,7 +26410,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="269" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2">
         <v>269</v>
       </c>
@@ -26487,7 +26487,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="270" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2">
         <v>270</v>
       </c>
@@ -26564,7 +26564,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="271" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2">
         <v>271</v>
       </c>
@@ -26641,7 +26641,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="272" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2">
         <v>272</v>
       </c>
@@ -26718,7 +26718,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="273" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2">
         <v>273</v>
       </c>
@@ -26795,7 +26795,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="274" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2">
         <v>274</v>
       </c>
@@ -26872,7 +26872,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="275" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2">
         <v>275</v>
       </c>
@@ -26949,7 +26949,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="276" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2">
         <v>276</v>
       </c>
@@ -27026,7 +27026,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="277" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2">
         <v>277</v>
       </c>
@@ -27103,7 +27103,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="278" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2">
         <v>278</v>
       </c>
@@ -27180,7 +27180,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="279" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2">
         <v>279</v>
       </c>
@@ -27257,7 +27257,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="280" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2">
         <v>280</v>
       </c>
@@ -27334,7 +27334,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="281" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2">
         <v>281</v>
       </c>
@@ -27411,7 +27411,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="282" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2">
         <v>282</v>
       </c>
@@ -27488,7 +27488,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="283" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2">
         <v>283</v>
       </c>
@@ -27565,7 +27565,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="284" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2">
         <v>284</v>
       </c>
@@ -27642,7 +27642,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="285" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2">
         <v>285</v>
       </c>
@@ -27719,7 +27719,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="286" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2">
         <v>286</v>
       </c>
@@ -27796,7 +27796,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="287" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2">
         <v>287</v>
       </c>
@@ -27873,7 +27873,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="288" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2">
         <v>288</v>
       </c>
@@ -27950,7 +27950,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="289" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2">
         <v>289</v>
       </c>
@@ -28027,7 +28027,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="290" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2">
         <v>290</v>
       </c>
@@ -28104,7 +28104,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="291" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2">
         <v>291</v>
       </c>
@@ -28181,7 +28181,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="292" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2">
         <v>292</v>
       </c>
@@ -28258,7 +28258,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="293" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2">
         <v>293</v>
       </c>
@@ -28335,7 +28335,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="294" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2">
         <v>294</v>
       </c>
@@ -28412,7 +28412,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="295" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2">
         <v>295</v>
       </c>
@@ -28489,7 +28489,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="296" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2">
         <v>296</v>
       </c>
@@ -28566,7 +28566,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="297" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2">
         <v>297</v>
       </c>
@@ -28643,7 +28643,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="298" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2">
         <v>298</v>
       </c>
@@ -28720,7 +28720,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="299" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2">
         <v>299</v>
       </c>

--- a/Versão5/ABNT/Ontologia_15965_0M.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_0M.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62029A8B-CA0E-47DF-BF03-CDCF1B5AE8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAE1F252-9DF0-46F2-A905-5E051D897841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8037" uniqueCount="909">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8037" uniqueCount="908">
   <si>
     <t>"Carbono"</t>
   </si>
@@ -2802,9 +2802,6 @@
   </si>
   <si>
     <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1.</t>
-  </si>
-  <si>
-    <t>Arquitetura</t>
   </si>
   <si>
     <t>[ 5I ]</t>
@@ -3295,63 +3292,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{A7FEC7FD-CB9A-4004-86BB-12C4E53E09F9}"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <font>
         <b val="0"/>
@@ -3998,7 +3939,7 @@
       </c>
       <c r="B18" s="14">
         <f ca="1">NOW()</f>
-        <v>46216.267614930555</v>
+        <v>46219.563504976853</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>664</v>
@@ -4285,7 +4226,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V2" s="39" t="s">
-        <v>903</v>
+        <v>646</v>
       </c>
       <c r="W2" s="58" t="str">
         <f>CONCATENATE("Key-ABNT-",A2)</f>
@@ -4298,7 +4239,7 @@
         <v>285</v>
       </c>
       <c r="Z2" s="39" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="AA2" s="39" t="str">
         <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
@@ -4356,7 +4297,7 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="39" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="Q3" s="39" t="s">
         <v>902</v>
@@ -4377,7 +4318,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V3" s="39" t="s">
-        <v>903</v>
+        <v>646</v>
       </c>
       <c r="W3" s="58" t="str">
         <f t="shared" ref="W3:W42" si="4">CONCATENATE("Key-ABNT-",A3)</f>
@@ -4448,7 +4389,7 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="39" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="Q4" s="39" t="s">
         <v>902</v>
@@ -4469,7 +4410,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V4" s="39" t="s">
-        <v>903</v>
+        <v>646</v>
       </c>
       <c r="W4" s="58" t="str">
         <f t="shared" si="4"/>
@@ -4540,7 +4481,7 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="39" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="Q5" s="39" t="s">
         <v>902</v>
@@ -4561,7 +4502,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V5" s="39" t="s">
-        <v>903</v>
+        <v>646</v>
       </c>
       <c r="W5" s="58" t="str">
         <f t="shared" si="4"/>
@@ -4632,7 +4573,7 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="39" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Q6" s="39" t="s">
         <v>902</v>
@@ -4653,7 +4594,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V6" s="39" t="s">
-        <v>903</v>
+        <v>646</v>
       </c>
       <c r="W6" s="58" t="str">
         <f t="shared" si="4"/>
@@ -7968,29 +7909,19 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A7:A42">
-    <cfRule type="cellIs" dxfId="17" priority="9" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA1 AA7:AA1048576">
-    <cfRule type="cellIs" dxfId="12" priority="7" operator="equal">
+  <conditionalFormatting sqref="A2:B42">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B6 B7:B42">
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+  <conditionalFormatting sqref="AA1:AA1048576">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8141,7 +8072,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8186,7 +8117,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8198,7 +8129,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79BA5E7-BFBD-4AC9-B36C-B9776AA17B75}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:Y299"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="5.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
@@ -8218,7 +8149,7 @@
     <col min="16" max="16" width="7.33203125" style="34" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="10" style="34" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6.83203125" style="34" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="25.83203125" style="34" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="32" style="34" customWidth="1"/>
     <col min="20" max="20" width="5" style="34" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="9.1640625" style="34" customWidth="1"/>
     <col min="22" max="22" width="5.83203125" style="34" bestFit="1" customWidth="1"/>
@@ -8305,7 +8236,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>2</v>
       </c>
@@ -8382,7 +8313,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -8459,7 +8390,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>4</v>
       </c>
@@ -8536,7 +8467,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>5</v>
       </c>
@@ -8613,7 +8544,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>6</v>
       </c>
@@ -8690,7 +8621,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>7</v>
       </c>
@@ -8767,7 +8698,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>8</v>
       </c>
@@ -8844,7 +8775,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>9</v>
       </c>
@@ -8921,7 +8852,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>10</v>
       </c>
@@ -8998,7 +8929,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>11</v>
       </c>
@@ -9075,7 +9006,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>12</v>
       </c>
@@ -9152,7 +9083,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>13</v>
       </c>
@@ -9229,7 +9160,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>14</v>
       </c>
@@ -9306,7 +9237,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>15</v>
       </c>
@@ -9383,7 +9314,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>16</v>
       </c>
@@ -9460,7 +9391,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>17</v>
       </c>
@@ -9537,7 +9468,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>18</v>
       </c>
@@ -9614,7 +9545,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>19</v>
       </c>
@@ -9691,7 +9622,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>20</v>
       </c>
@@ -9768,7 +9699,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>21</v>
       </c>
@@ -9845,7 +9776,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>22</v>
       </c>
@@ -9922,7 +9853,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>23</v>
       </c>
@@ -9999,7 +9930,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>24</v>
       </c>
@@ -10076,7 +10007,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>25</v>
       </c>
@@ -10153,7 +10084,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>26</v>
       </c>
@@ -10230,7 +10161,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>27</v>
       </c>
@@ -10307,7 +10238,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>28</v>
       </c>
@@ -10384,7 +10315,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>29</v>
       </c>
@@ -10461,7 +10392,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>30</v>
       </c>
@@ -10538,7 +10469,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>31</v>
       </c>
@@ -10615,7 +10546,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>32</v>
       </c>
@@ -10692,7 +10623,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>33</v>
       </c>
@@ -10769,7 +10700,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>34</v>
       </c>
@@ -10846,7 +10777,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>35</v>
       </c>
@@ -10923,7 +10854,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>36</v>
       </c>
@@ -11000,7 +10931,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>37</v>
       </c>
@@ -11077,7 +11008,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>38</v>
       </c>
@@ -11154,7 +11085,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>39</v>
       </c>
@@ -11231,7 +11162,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>40</v>
       </c>
@@ -11308,7 +11239,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>41</v>
       </c>
@@ -11385,7 +11316,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>42</v>
       </c>
@@ -11462,7 +11393,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>43</v>
       </c>
@@ -11539,7 +11470,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>44</v>
       </c>
@@ -11616,7 +11547,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>45</v>
       </c>
@@ -11693,7 +11624,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>46</v>
       </c>
@@ -11770,7 +11701,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>47</v>
       </c>
@@ -11847,7 +11778,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>48</v>
       </c>
@@ -11924,7 +11855,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>49</v>
       </c>
@@ -12001,7 +11932,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>50</v>
       </c>
@@ -12078,7 +12009,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>51</v>
       </c>
@@ -12155,7 +12086,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>52</v>
       </c>
@@ -12232,7 +12163,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>53</v>
       </c>
@@ -12309,7 +12240,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>54</v>
       </c>
@@ -12386,7 +12317,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>55</v>
       </c>
@@ -12463,7 +12394,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>56</v>
       </c>
@@ -12540,7 +12471,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>57</v>
       </c>
@@ -12617,7 +12548,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>58</v>
       </c>
@@ -12694,7 +12625,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>59</v>
       </c>
@@ -12771,7 +12702,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>60</v>
       </c>
@@ -12848,7 +12779,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>61</v>
       </c>
@@ -12925,7 +12856,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>62</v>
       </c>
@@ -13002,7 +12933,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>63</v>
       </c>
@@ -13079,7 +13010,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>64</v>
       </c>
@@ -13156,7 +13087,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>65</v>
       </c>
@@ -13233,7 +13164,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>66</v>
       </c>
@@ -13310,7 +13241,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>67</v>
       </c>
@@ -13387,7 +13318,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>68</v>
       </c>
@@ -13464,7 +13395,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>69</v>
       </c>
@@ -13541,7 +13472,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>70</v>
       </c>
@@ -13618,7 +13549,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>71</v>
       </c>
@@ -13695,7 +13626,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>72</v>
       </c>
@@ -13772,7 +13703,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>73</v>
       </c>
@@ -13849,7 +13780,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>74</v>
       </c>
@@ -13926,7 +13857,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>75</v>
       </c>
@@ -14003,7 +13934,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>76</v>
       </c>
@@ -14080,7 +14011,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>77</v>
       </c>
@@ -14157,7 +14088,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>78</v>
       </c>
@@ -14234,7 +14165,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>79</v>
       </c>
@@ -14311,7 +14242,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>80</v>
       </c>
@@ -14388,7 +14319,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>81</v>
       </c>
@@ -14465,7 +14396,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>82</v>
       </c>
@@ -14542,7 +14473,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <v>83</v>
       </c>
@@ -14619,7 +14550,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <v>84</v>
       </c>
@@ -14696,7 +14627,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>85</v>
       </c>
@@ -14773,7 +14704,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>86</v>
       </c>
@@ -14850,7 +14781,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>87</v>
       </c>
@@ -14927,7 +14858,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>88</v>
       </c>
@@ -15004,7 +14935,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>89</v>
       </c>
@@ -15081,7 +15012,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>90</v>
       </c>
@@ -15158,7 +15089,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>91</v>
       </c>
@@ -15235,7 +15166,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>92</v>
       </c>
@@ -15312,7 +15243,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>93</v>
       </c>
@@ -15389,7 +15320,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>94</v>
       </c>
@@ -15466,7 +15397,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>95</v>
       </c>
@@ -15543,7 +15474,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>96</v>
       </c>
@@ -15620,7 +15551,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>97</v>
       </c>
@@ -15697,7 +15628,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>98</v>
       </c>
@@ -15774,7 +15705,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>99</v>
       </c>
@@ -15851,7 +15782,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>100</v>
       </c>
@@ -15928,7 +15859,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <v>101</v>
       </c>
@@ -16005,7 +15936,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <v>102</v>
       </c>
@@ -16082,7 +16013,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>103</v>
       </c>
@@ -16159,7 +16090,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
         <v>104</v>
       </c>
@@ -16236,7 +16167,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
         <v>105</v>
       </c>
@@ -16313,7 +16244,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
         <v>106</v>
       </c>
@@ -16390,7 +16321,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
         <v>107</v>
       </c>
@@ -16467,7 +16398,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
         <v>108</v>
       </c>
@@ -16544,7 +16475,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
         <v>109</v>
       </c>
@@ -16621,7 +16552,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
         <v>110</v>
       </c>
@@ -16698,7 +16629,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
         <v>111</v>
       </c>
@@ -16775,7 +16706,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
         <v>112</v>
       </c>
@@ -16852,7 +16783,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
         <v>113</v>
       </c>
@@ -16929,7 +16860,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
         <v>114</v>
       </c>
@@ -17006,7 +16937,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
         <v>115</v>
       </c>
@@ -17083,7 +17014,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
         <v>116</v>
       </c>
@@ -17160,7 +17091,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="2">
         <v>117</v>
       </c>
@@ -17237,7 +17168,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="2">
         <v>118</v>
       </c>
@@ -17314,7 +17245,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="2">
         <v>119</v>
       </c>
@@ -17391,7 +17322,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="2">
         <v>120</v>
       </c>
@@ -17468,7 +17399,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="2">
         <v>121</v>
       </c>
@@ -17545,7 +17476,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="2">
         <v>122</v>
       </c>
@@ -17622,7 +17553,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="123" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="2">
         <v>123</v>
       </c>
@@ -17699,7 +17630,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="2">
         <v>124</v>
       </c>
@@ -17776,7 +17707,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="2">
         <v>125</v>
       </c>
@@ -17853,7 +17784,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="2">
         <v>126</v>
       </c>
@@ -17930,7 +17861,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="2">
         <v>127</v>
       </c>
@@ -18007,7 +17938,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="2">
         <v>128</v>
       </c>
@@ -18084,7 +18015,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="129" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="2">
         <v>129</v>
       </c>
@@ -18161,7 +18092,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="130" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="2">
         <v>130</v>
       </c>
@@ -18238,7 +18169,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="131" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="2">
         <v>131</v>
       </c>
@@ -18315,7 +18246,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="132" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="2">
         <v>132</v>
       </c>
@@ -18392,7 +18323,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="133" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="2">
         <v>133</v>
       </c>
@@ -18469,7 +18400,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="134" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="2">
         <v>134</v>
       </c>
@@ -18546,7 +18477,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="135" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="2">
         <v>135</v>
       </c>
@@ -18623,7 +18554,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="2">
         <v>136</v>
       </c>
@@ -18700,7 +18631,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="2">
         <v>137</v>
       </c>
@@ -18777,7 +18708,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="2">
         <v>138</v>
       </c>
@@ -18854,7 +18785,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="2">
         <v>139</v>
       </c>
@@ -18931,7 +18862,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="2">
         <v>140</v>
       </c>
@@ -19008,7 +18939,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="2">
         <v>141</v>
       </c>
@@ -19085,7 +19016,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="142" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="2">
         <v>142</v>
       </c>
@@ -19162,7 +19093,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="143" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="2">
         <v>143</v>
       </c>
@@ -19239,7 +19170,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="144" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="2">
         <v>144</v>
       </c>
@@ -19316,7 +19247,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="2">
         <v>145</v>
       </c>
@@ -19393,7 +19324,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="146" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="2">
         <v>146</v>
       </c>
@@ -19470,7 +19401,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="147" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="2">
         <v>147</v>
       </c>
@@ -19547,7 +19478,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="148" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="2">
         <v>148</v>
       </c>
@@ -19624,7 +19555,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="149" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="2">
         <v>149</v>
       </c>
@@ -19701,7 +19632,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="2">
         <v>150</v>
       </c>
@@ -19778,7 +19709,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="151" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="2">
         <v>151</v>
       </c>
@@ -19855,7 +19786,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="152" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="2">
         <v>152</v>
       </c>
@@ -19932,7 +19863,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="153" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="2">
         <v>153</v>
       </c>
@@ -20009,7 +19940,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="2">
         <v>154</v>
       </c>
@@ -20086,7 +20017,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="155" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="2">
         <v>155</v>
       </c>
@@ -20163,7 +20094,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="156" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="2">
         <v>156</v>
       </c>
@@ -20240,7 +20171,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="157" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="2">
         <v>157</v>
       </c>
@@ -20317,7 +20248,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="158" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="2">
         <v>158</v>
       </c>
@@ -20394,7 +20325,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="159" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="2">
         <v>159</v>
       </c>
@@ -20471,7 +20402,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="160" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="2">
         <v>160</v>
       </c>
@@ -20548,7 +20479,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="161" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="2">
         <v>161</v>
       </c>
@@ -20625,7 +20556,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="162" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="2">
         <v>162</v>
       </c>
@@ -20702,7 +20633,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="163" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="2">
         <v>163</v>
       </c>
@@ -20779,7 +20710,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="164" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="2">
         <v>164</v>
       </c>
@@ -20856,7 +20787,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="165" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="2">
         <v>165</v>
       </c>
@@ -20933,7 +20864,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="166" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="2">
         <v>166</v>
       </c>
@@ -21010,7 +20941,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="167" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="2">
         <v>167</v>
       </c>
@@ -21087,7 +21018,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="168" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="2">
         <v>168</v>
       </c>
@@ -21164,7 +21095,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="169" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="2">
         <v>169</v>
       </c>
@@ -21241,7 +21172,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="170" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="2">
         <v>170</v>
       </c>
@@ -21318,7 +21249,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="171" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="2">
         <v>171</v>
       </c>
@@ -21395,7 +21326,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="172" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="2">
         <v>172</v>
       </c>
@@ -21472,7 +21403,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="173" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="2">
         <v>173</v>
       </c>
@@ -21549,7 +21480,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="174" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="2">
         <v>174</v>
       </c>
@@ -21626,7 +21557,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="175" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="2">
         <v>175</v>
       </c>
@@ -21703,7 +21634,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="176" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="2">
         <v>176</v>
       </c>
@@ -21780,7 +21711,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="177" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="2">
         <v>177</v>
       </c>
@@ -21857,7 +21788,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="178" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="2">
         <v>178</v>
       </c>
@@ -21934,7 +21865,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="179" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="2">
         <v>179</v>
       </c>
@@ -22011,7 +21942,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="180" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="2">
         <v>180</v>
       </c>
@@ -22088,7 +22019,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="181" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="2">
         <v>181</v>
       </c>
@@ -22165,7 +22096,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="182" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="2">
         <v>182</v>
       </c>
@@ -22242,7 +22173,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="183" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="2">
         <v>183</v>
       </c>
@@ -22319,7 +22250,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="184" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="2">
         <v>184</v>
       </c>
@@ -22396,7 +22327,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="185" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="2">
         <v>185</v>
       </c>
@@ -22473,7 +22404,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="186" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="2">
         <v>186</v>
       </c>
@@ -22550,7 +22481,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="187" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="2">
         <v>187</v>
       </c>
@@ -22627,7 +22558,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="188" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="2">
         <v>188</v>
       </c>
@@ -22704,7 +22635,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="189" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="2">
         <v>189</v>
       </c>
@@ -22781,7 +22712,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="190" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="2">
         <v>190</v>
       </c>
@@ -22858,7 +22789,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="191" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="2">
         <v>191</v>
       </c>
@@ -22935,7 +22866,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="192" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="2">
         <v>192</v>
       </c>
@@ -23012,7 +22943,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="193" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="2">
         <v>193</v>
       </c>
@@ -23089,7 +23020,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="194" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="2">
         <v>194</v>
       </c>
@@ -23166,7 +23097,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="195" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="2">
         <v>195</v>
       </c>
@@ -23243,7 +23174,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="196" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="2">
         <v>196</v>
       </c>
@@ -23320,7 +23251,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="197" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="2">
         <v>197</v>
       </c>
@@ -23397,7 +23328,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="198" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="2">
         <v>198</v>
       </c>
@@ -23474,7 +23405,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="199" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="2">
         <v>199</v>
       </c>
@@ -23551,7 +23482,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="200" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="2">
         <v>200</v>
       </c>
@@ -23628,7 +23559,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="201" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="2">
         <v>201</v>
       </c>
@@ -23705,7 +23636,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="202" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="2">
         <v>202</v>
       </c>
@@ -23782,7 +23713,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="203" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="2">
         <v>203</v>
       </c>
@@ -23859,7 +23790,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="204" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="2">
         <v>204</v>
       </c>
@@ -23936,7 +23867,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="205" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="2">
         <v>205</v>
       </c>
@@ -24013,7 +23944,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="206" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="2">
         <v>206</v>
       </c>
@@ -24090,7 +24021,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="207" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="2">
         <v>207</v>
       </c>
@@ -24167,7 +24098,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="208" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="2">
         <v>208</v>
       </c>
@@ -24244,7 +24175,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="209" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="2">
         <v>209</v>
       </c>
@@ -24321,7 +24252,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="210" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="2">
         <v>210</v>
       </c>
@@ -24398,7 +24329,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="211" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="2">
         <v>211</v>
       </c>
@@ -24475,7 +24406,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="212" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="2">
         <v>212</v>
       </c>
@@ -24552,7 +24483,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="213" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="2">
         <v>213</v>
       </c>
@@ -24629,7 +24560,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="214" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="2">
         <v>214</v>
       </c>
@@ -24706,7 +24637,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="215" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="2">
         <v>215</v>
       </c>
@@ -24783,7 +24714,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="216" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="2">
         <v>216</v>
       </c>
@@ -24860,7 +24791,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="217" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="2">
         <v>217</v>
       </c>
@@ -24937,7 +24868,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="218" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="2">
         <v>218</v>
       </c>
@@ -25014,7 +24945,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="219" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="2">
         <v>219</v>
       </c>
@@ -25091,7 +25022,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="220" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="2">
         <v>220</v>
       </c>
@@ -25168,7 +25099,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="221" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="2">
         <v>221</v>
       </c>
@@ -25245,7 +25176,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="222" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="2">
         <v>222</v>
       </c>
@@ -25322,7 +25253,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="223" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="2">
         <v>223</v>
       </c>
@@ -25399,7 +25330,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="224" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="2">
         <v>224</v>
       </c>
@@ -25476,7 +25407,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="225" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="2">
         <v>225</v>
       </c>
@@ -25553,7 +25484,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="226" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="2">
         <v>226</v>
       </c>
@@ -25630,7 +25561,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="227" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="2">
         <v>227</v>
       </c>
@@ -25707,7 +25638,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="228" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="2">
         <v>228</v>
       </c>
@@ -25784,7 +25715,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="229" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="2">
         <v>229</v>
       </c>
@@ -25861,7 +25792,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="230" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="2">
         <v>230</v>
       </c>
@@ -25938,7 +25869,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="231" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="2">
         <v>231</v>
       </c>
@@ -26015,7 +25946,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="232" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="2">
         <v>232</v>
       </c>
@@ -26092,7 +26023,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="233" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="2">
         <v>233</v>
       </c>
@@ -26169,7 +26100,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="234" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="2">
         <v>234</v>
       </c>
@@ -26246,7 +26177,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="235" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="2">
         <v>235</v>
       </c>
@@ -26323,7 +26254,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="236" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="2">
         <v>236</v>
       </c>
@@ -26400,7 +26331,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="237" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="2">
         <v>237</v>
       </c>
@@ -26477,7 +26408,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="238" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="2">
         <v>238</v>
       </c>
@@ -26554,7 +26485,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="239" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="2">
         <v>239</v>
       </c>
@@ -26631,7 +26562,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="240" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="2">
         <v>240</v>
       </c>
@@ -26708,7 +26639,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="241" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="2">
         <v>241</v>
       </c>
@@ -26785,7 +26716,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="242" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="2">
         <v>242</v>
       </c>
@@ -26862,7 +26793,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="243" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="2">
         <v>243</v>
       </c>
@@ -26939,7 +26870,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="244" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="2">
         <v>244</v>
       </c>
@@ -27016,7 +26947,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="245" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="2">
         <v>245</v>
       </c>
@@ -27093,7 +27024,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="246" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="2">
         <v>246</v>
       </c>
@@ -27170,7 +27101,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="247" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="2">
         <v>247</v>
       </c>
@@ -27247,7 +27178,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="248" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="2">
         <v>248</v>
       </c>
@@ -27324,7 +27255,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="249" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="2">
         <v>249</v>
       </c>
@@ -27401,7 +27332,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="250" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="2">
         <v>250</v>
       </c>
@@ -27478,7 +27409,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="251" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="2">
         <v>251</v>
       </c>
@@ -27555,7 +27486,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="252" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="2">
         <v>252</v>
       </c>
@@ -27632,7 +27563,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="253" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="2">
         <v>253</v>
       </c>
@@ -27709,7 +27640,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="254" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="2">
         <v>254</v>
       </c>
@@ -27786,7 +27717,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="255" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="2">
         <v>255</v>
       </c>
@@ -27863,7 +27794,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="256" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="2">
         <v>256</v>
       </c>
@@ -27940,7 +27871,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="257" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="2">
         <v>257</v>
       </c>
@@ -28017,7 +27948,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="258" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="2">
         <v>258</v>
       </c>
@@ -28094,7 +28025,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="259" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="2">
         <v>259</v>
       </c>
@@ -28171,7 +28102,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="260" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="2">
         <v>260</v>
       </c>
@@ -28248,7 +28179,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="261" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="2">
         <v>261</v>
       </c>
@@ -28325,7 +28256,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="262" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="2">
         <v>262</v>
       </c>
@@ -28402,7 +28333,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="263" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="2">
         <v>263</v>
       </c>
@@ -28479,7 +28410,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="264" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="2">
         <v>264</v>
       </c>
@@ -28556,7 +28487,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="265" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="2">
         <v>265</v>
       </c>
@@ -28633,7 +28564,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="266" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="2">
         <v>266</v>
       </c>
@@ -28710,7 +28641,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="267" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="2">
         <v>267</v>
       </c>
@@ -28787,7 +28718,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="268" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="2">
         <v>268</v>
       </c>
@@ -28864,7 +28795,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="269" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="2">
         <v>269</v>
       </c>
@@ -28941,7 +28872,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="270" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="2">
         <v>270</v>
       </c>
@@ -29018,7 +28949,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="271" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="2">
         <v>271</v>
       </c>
@@ -29095,7 +29026,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="272" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="2">
         <v>272</v>
       </c>
@@ -29172,7 +29103,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="273" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="2">
         <v>273</v>
       </c>
@@ -29249,7 +29180,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="274" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="2">
         <v>274</v>
       </c>
@@ -29326,7 +29257,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="275" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="2">
         <v>275</v>
       </c>
@@ -29403,7 +29334,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="276" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="2">
         <v>276</v>
       </c>
@@ -29480,7 +29411,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="277" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="2">
         <v>277</v>
       </c>
@@ -29557,7 +29488,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="278" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="2">
         <v>278</v>
       </c>
@@ -29634,7 +29565,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="279" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="2">
         <v>279</v>
       </c>
@@ -29711,7 +29642,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="280" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="2">
         <v>280</v>
       </c>
@@ -29788,7 +29719,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="281" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="2">
         <v>281</v>
       </c>
@@ -29865,7 +29796,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="282" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="2">
         <v>282</v>
       </c>
@@ -29942,7 +29873,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="283" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="2">
         <v>283</v>
       </c>
@@ -30019,7 +29950,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="284" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="2">
         <v>284</v>
       </c>
@@ -30096,7 +30027,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="285" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="2">
         <v>285</v>
       </c>
@@ -30173,7 +30104,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="286" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="2">
         <v>286</v>
       </c>
@@ -30250,7 +30181,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="287" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="2">
         <v>287</v>
       </c>
@@ -30327,7 +30258,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="288" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="2">
         <v>288</v>
       </c>
@@ -30404,7 +30335,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="289" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="2">
         <v>289</v>
       </c>
@@ -30481,7 +30412,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="290" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="2">
         <v>290</v>
       </c>
@@ -30558,7 +30489,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="291" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="2">
         <v>291</v>
       </c>
@@ -30635,7 +30566,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="292" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="2">
         <v>292</v>
       </c>
@@ -30712,7 +30643,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="293" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="2">
         <v>293</v>
       </c>
@@ -30789,7 +30720,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="294" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="2">
         <v>294</v>
       </c>
@@ -30866,7 +30797,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="295" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="2">
         <v>295</v>
       </c>
@@ -30943,7 +30874,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="296" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="2">
         <v>296</v>
       </c>
@@ -31020,7 +30951,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="297" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="2">
         <v>297</v>
       </c>
@@ -31097,7 +31028,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="298" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="2">
         <v>298</v>
       </c>
@@ -31174,7 +31105,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="299" spans="1:25" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="2">
         <v>299</v>
       </c>
@@ -31254,16 +31185,16 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1:Y1048576 P2:W5">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_0M.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_0M.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD2C4BF-8905-4D7F-BD89-933170A2B073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAFE511A-3C59-4144-B92B-81A6DD32C836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8037" uniqueCount="914">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8076" uniqueCount="940">
   <si>
     <t>"Carbono"</t>
   </si>
@@ -2835,13 +2835,91 @@
   </si>
   <si>
     <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 5I. Building Information Codes.</t>
+  </si>
+  <si>
+    <t>Fonte1</t>
+  </si>
+  <si>
+    <t>https://brasil.un.org/pt-br/sdgs</t>
+  </si>
+  <si>
+    <t>Fonte2</t>
+  </si>
+  <si>
+    <t>https://eaesp.fgv.br/centros/centro-estudos-sustentabilidade/projetos/programa-brasileiro-ghg-protocol</t>
+  </si>
+  <si>
+    <t>Fonte3</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/acesso-a-informacao/acoes-e-programas/transformacao-ecologica/transformacao-ecologica</t>
+  </si>
+  <si>
+    <t>FonteVegetação1</t>
+  </si>
+  <si>
+    <t>https://museunacional.ufrj.br/hortobotanico</t>
+  </si>
+  <si>
+    <t>FonteVegetação2</t>
+  </si>
+  <si>
+    <t>https://www.embrapa.br/florestas/publicacoes</t>
+  </si>
+  <si>
+    <t>FonteVegetação3</t>
+  </si>
+  <si>
+    <t>https://www.arvoresgigantes.org</t>
+  </si>
+  <si>
+    <t>FonteVegetação4</t>
+  </si>
+  <si>
+    <t>https://www.scielo.br/j/abb</t>
+  </si>
+  <si>
+    <t>FonteVegetação5</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/inpa/pt-br/Pesquisa/colecoes/botanica</t>
+  </si>
+  <si>
+    <t>FonteVegetação6</t>
+  </si>
+  <si>
+    <t>https://botanicasaopaulo.org</t>
+  </si>
+  <si>
+    <t>FonteVegetação7</t>
+  </si>
+  <si>
+    <t>https://pesquisa.in.gov.br/imprensa</t>
+  </si>
+  <si>
+    <t>FonteVegetação8</t>
+  </si>
+  <si>
+    <t>https://mapas.florestal.gov.br</t>
+  </si>
+  <si>
+    <t>FonteTSB</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/orgaos/spe/taxonomia-sustentavel-brasileira/cadernos</t>
+  </si>
+  <si>
+    <t>FonteSINAPI</t>
+  </si>
+  <si>
+    <t>https://www.caixa.gov.br/site/Paginas/downloads.aspx#categoria_888</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="8"/>
       <color theme="1"/>
@@ -2929,8 +3007,34 @@
       <name val="Arial Nova Cond"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <color theme="10"/>
+      <name val="Arial Nova Cond Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial Nova Cond"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="6"/>
+      <color theme="10"/>
+      <name val="Arial Nova Cond Light"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="25">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3075,6 +3179,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -3124,11 +3234,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3305,38 +3416,31 @@
     <xf numFmtId="0" fontId="7" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="17" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hiperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{A7FEC7FD-CB9A-4004-86BB-12C4E53E09F9}"/>
   </cellStyles>
-  <dxfs count="15">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="13">
     <dxf>
       <font>
         <b val="0"/>
@@ -3395,6 +3499,16 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3780,7 +3894,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F29EE3D7-EE2C-4826-A6E3-4917652068E2}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
@@ -3983,7 +4097,7 @@
       </c>
       <c r="B18" s="14">
         <f ca="1">NOW()</f>
-        <v>46232.779937847219</v>
+        <v>46233.480470486109</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>663</v>
@@ -4079,7 +4193,157 @@
         <v>665</v>
       </c>
     </row>
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="41" t="s">
+        <v>914</v>
+      </c>
+      <c r="B27" s="60" t="s">
+        <v>915</v>
+      </c>
+      <c r="C27" s="44" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="41" t="s">
+        <v>916</v>
+      </c>
+      <c r="B28" s="61" t="s">
+        <v>917</v>
+      </c>
+      <c r="C28" s="44" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="41" t="s">
+        <v>918</v>
+      </c>
+      <c r="B29" s="61" t="s">
+        <v>919</v>
+      </c>
+      <c r="C29" s="44" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="41" t="s">
+        <v>920</v>
+      </c>
+      <c r="B30" s="62" t="s">
+        <v>921</v>
+      </c>
+      <c r="C30" s="44" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="41" t="s">
+        <v>922</v>
+      </c>
+      <c r="B31" s="62" t="s">
+        <v>923</v>
+      </c>
+      <c r="C31" s="44" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="41" t="s">
+        <v>924</v>
+      </c>
+      <c r="B32" s="62" t="s">
+        <v>925</v>
+      </c>
+      <c r="C32" s="44" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="41" t="s">
+        <v>926</v>
+      </c>
+      <c r="B33" s="64" t="s">
+        <v>927</v>
+      </c>
+      <c r="C33" s="44" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="41" t="s">
+        <v>928</v>
+      </c>
+      <c r="B34" s="64" t="s">
+        <v>929</v>
+      </c>
+      <c r="C34" s="44" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="41" t="s">
+        <v>930</v>
+      </c>
+      <c r="B35" s="62" t="s">
+        <v>931</v>
+      </c>
+      <c r="C35" s="44" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="41" t="s">
+        <v>932</v>
+      </c>
+      <c r="B36" s="64" t="s">
+        <v>933</v>
+      </c>
+      <c r="C36" s="44" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="41" t="s">
+        <v>934</v>
+      </c>
+      <c r="B37" s="62" t="s">
+        <v>935</v>
+      </c>
+      <c r="C37" s="44" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="13" t="s">
+        <v>936</v>
+      </c>
+      <c r="B38" s="65" t="s">
+        <v>937</v>
+      </c>
+      <c r="C38" s="44" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" s="67" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="41" t="s">
+        <v>938</v>
+      </c>
+      <c r="B39" s="66" t="s">
+        <v>939</v>
+      </c>
+      <c r="C39" s="44" t="s">
+        <v>663</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B27" r:id="rId1" xr:uid="{E4986F19-EB69-4FD2-9F21-F31C4FCD4E69}"/>
+    <hyperlink ref="B29" r:id="rId2" xr:uid="{BA6A2C29-CA80-495D-8A5B-3F6EB787C5CF}"/>
+    <hyperlink ref="B28" r:id="rId3" xr:uid="{0753A972-1E32-47FB-ACEB-B206917DE0EC}"/>
+    <hyperlink ref="B38" r:id="rId4" xr:uid="{A92F85B0-AADB-4E54-B6DE-D96D3070328D}"/>
+    <hyperlink ref="B39" r:id="rId5" location="categoria_888" xr:uid="{A67C0138-CEC4-431A-A344-2306DE2C1FB1}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -5880,7 +6144,7 @@
         <v>Normativo</v>
       </c>
       <c r="M20" s="49" t="str">
-        <f t="shared" ref="M18:M20" si="9">CONCATENATE("", D20)</f>
+        <f t="shared" ref="M20" si="9">CONCATENATE("", D20)</f>
         <v>NBR.Temática</v>
       </c>
       <c r="N20" s="49" t="str">
@@ -5967,7 +6231,7 @@
         <v>285</v>
       </c>
       <c r="L21" s="49" t="str">
-        <f t="shared" ref="L18:M34" si="15">CONCATENATE("", C21)</f>
+        <f t="shared" ref="L21:M34" si="15">CONCATENATE("", C21)</f>
         <v>Normativo</v>
       </c>
       <c r="M21" s="49" t="str">
@@ -7953,32 +8217,22 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B6 A20:B42">
-    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
+  <conditionalFormatting sqref="A2:B42">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="13" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA6 AA20:AA1048576">
-    <cfRule type="cellIs" dxfId="9" priority="9" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A7:B19">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
+    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F19">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA7:AA19">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+  <conditionalFormatting sqref="AA1:AA1048576">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8129,7 +8383,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8174,7 +8428,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -31242,16 +31496,16 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1:Y1048576 P2:W5">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
